--- a/mlef_pipeline/results/OS_6/HIGH_PDL1/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_6/HIGH_PDL1/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,799 +548,284 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD</t>
+          <t>RWD_FMRAD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7070540005654511</v>
+        <v>0.8218432510885341</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05243956106106173</v>
+        <v>0.07103369217978195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5231086246602653</v>
+        <v>0.6725252143594443</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06370432776423926</v>
+        <v>0.04976280497231454</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5583676177632927</v>
+        <v>0.7917939764295068</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1912794688424858</v>
+        <v>0.1405865825907438</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6514813113415293</v>
+        <v>0.6269068484258358</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2584146003422291</v>
+        <v>0.184198400342047</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6993197278911565</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1572693271638526</v>
+        <v>0.2494158561708674</v>
       </c>
       <c r="L2" t="n">
-        <v>0.571619812583668</v>
+        <v>0.4591104734576757</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5918367346938775</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6706730769230766</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1469971708320201</v>
+        <v>0.3254563327840967</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.571619812583668</v>
+        <v>0.4886363636363636</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5576923076923077</v>
+        <v>0.64</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.4</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U2" t="n">
-        <v>401</v>
+        <v>158</v>
       </c>
       <c r="V2" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_DP</t>
+          <t>RWD_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7556867891513561</v>
+        <v>0.6514876632801163</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06981160935154018</v>
+        <v>0.09281390242852272</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5849325104403529</v>
+        <v>0.3045709504133773</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09491602406870002</v>
+        <v>0.1666382045763946</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6728206911912324</v>
+        <v>0.4164556962025316</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2160431081603065</v>
+        <v>0.470370276914116</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6442629815745394</v>
+        <v>0.6518987341772152</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2498510747220077</v>
+        <v>0.4763683181692079</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="K3" t="n">
-        <v>0.259465368043459</v>
+        <v>0.2826729697967488</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5241228070175439</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="M3" t="n">
-        <v>0.48</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0.641414141414141</v>
+        <v>0.6479999999999997</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2264805304534893</v>
+        <v>0.317780221974885</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4378860672614963</v>
+        <v>0.6103896103896104</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.84</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.4</v>
       </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="V3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="W3" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP/rwd-only</t>
+          <t>RWD_DP_FMRAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6979440069991252</v>
+        <v>0.9066820276497696</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07505202529612598</v>
+        <v>0.05962995200565036</v>
       </c>
       <c r="D4" t="n">
-        <v>0.356251170091123</v>
+        <v>0.7235192504757723</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1053703527780178</v>
+        <v>0.1117577387166165</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4472819470759993</v>
+        <v>0.6705128205128206</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4001221754651369</v>
+        <v>0.07119224832931163</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5951184493898062</v>
+        <v>0.8962962962962964</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3883472382459242</v>
+        <v>0.1141885821712992</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8399999999999999</v>
+        <v>0.1666666666666665</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2086202599639456</v>
+        <v>0.2390035292236633</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7472826086956521</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.8888888888888884</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.1188518344736996</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>0.6637931034482758</v>
+        <v>0.3448275862068966</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4" t="n">
-        <v>199</v>
+        <v>90</v>
       </c>
       <c r="V4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="W4" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8271183473389354</v>
+        <v>0.6437211981566819</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06619066906511739</v>
+        <v>0.1143470001609829</v>
       </c>
       <c r="D5" t="n">
-        <v>0.565733275034726</v>
+        <v>0.2318664717348928</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1492357092125044</v>
+        <v>0.06303728097254005</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8341109760380913</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1490478831986918</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5441739780548409</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3851578332529429</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4679487179487176</v>
+        <v>0.964285714285714</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3313243281365976</v>
+        <v>0.0528564997239297</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4793491864831039</v>
+        <v>0.2245614035087719</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.2651515151515154</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.2059570647145375</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>0.3665158371040724</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U5" t="n">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="V5" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RWD_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.6755077030812324</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.08763626061997898</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3053150697263284</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.1339477875439441</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6248418177971806</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.4029577629051871</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.3601908657123382</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.4109495361313424</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.6474358974358974</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.2617871933120599</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.4420512820512821</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.4230769230769231</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.4090909090909089</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.332028761846765</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.1979166666666667</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.04545454545454546</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" t="n">
-        <v>163</v>
-      </c>
-      <c r="V6" t="n">
-        <v>32</v>
-      </c>
-      <c r="W6" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.7522404779686331</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.07815451664564932</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.602711662892122</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.0486987414870164</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6568839451242121</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.1976032561388378</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.6809484422387648</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.2218914893256626</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.5654761904761905</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.2499259533753824</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5421052631578948</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.6190476190476191</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.5760000000000001</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.2180645277322724</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.4993581514762516</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>155</v>
-      </c>
-      <c r="V7" t="n">
-        <v>29</v>
-      </c>
-      <c r="W7" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.682972367438387</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.08800145678828697</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.4244405036895489</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.09403454506880121</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.4968997651711779</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.3115974576594775</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6162117452440034</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.4027327264529616</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.5654761904761905</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.3009531233051095</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5695006747638327</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.7280000000000002</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.2734585590376998</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.6103896103896104</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U8" t="n">
-        <v>155</v>
-      </c>
-      <c r="V8" t="n">
-        <v>29</v>
-      </c>
-      <c r="W8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.9460869565217391</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.04741894651349798</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.7988534615780852</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.09759638731412537</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.692475320310859</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.2182767895574467</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6190476190476191</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.4074364963296424</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.4711111111111111</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.6361407203581044</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.3066666666666666</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="T9" t="n">
-        <v>12</v>
-      </c>
-      <c r="U9" t="n">
-        <v>71</v>
-      </c>
-      <c r="V9" t="n">
-        <v>17</v>
-      </c>
-      <c r="W9" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.6269565217391304</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.134692830811469</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2056417108509418</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0865829639485251</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.4841549295774648</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.4751434074960599</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.4178403755868545</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.456969365629815</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.785714285714286</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2247013741241746</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.6136363636363636</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.4117647058823528</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.5134486604426787</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.3406593406593407</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="T10" t="n">
-        <v>7</v>
-      </c>
-      <c r="U10" t="n">
-        <v>71</v>
-      </c>
-      <c r="V10" t="n">
-        <v>17</v>
-      </c>
-      <c r="W10" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.8011904761904762</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.102151981149015</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.6367188501795004</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.06929325677001812</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.6790956439393939</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.1889859701064079</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.7601239669421488</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.2584585771885022</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.3556318101242262</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.4333333333333333</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.7222222222222214</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>0.391025641025641</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>11</v>
-      </c>
-      <c r="U11" t="n">
-        <v>88</v>
-      </c>
-      <c r="V11" t="n">
-        <v>17</v>
-      </c>
-      <c r="W11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.4276785714285716</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.1248963031893712</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.2464844523668053</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.07415662438071581</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.3181818181818182</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.4657704893617999</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.6818181818181818</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.4657704893617999</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.785714285714286</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.1345051775866548</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>88</v>
-      </c>
-      <c r="V12" t="n">
-        <v>17</v>
-      </c>
-      <c r="W12" t="n">
         <v>19</v>
       </c>
     </row>

--- a/mlef_pipeline/results/OS_6/HIGH_PDL1/training_summary.xlsx
+++ b/mlef_pipeline/results/OS_6/HIGH_PDL1/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,284 +548,787 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8218432510885341</v>
+        <v>0.7127367825841109</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07103369217978195</v>
+        <v>0.05022850447827953</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6725252143594443</v>
+        <v>0.5479657382914899</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04976280497231454</v>
+        <v>0.06502323554244402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7917939764295068</v>
+        <v>0.6495948839338547</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1405865825907438</v>
+        <v>0.1765113393626718</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6269068484258358</v>
+        <v>0.5790658587449504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.184198400342047</v>
+        <v>0.2833845755150824</v>
       </c>
       <c r="J2" t="n">
+        <v>0.6462585034013604</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1676294227808608</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4497666421026775</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3469387755102041</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.7636217948717947</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1458528425349003</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.725557461406518</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="S2" t="n">
         <v>0.5</v>
       </c>
-      <c r="K2" t="n">
-        <v>0.2494158561708674</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.4591104734576757</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.3254563327840967</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.4886363636363636</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.4</v>
-      </c>
       <c r="T2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U2" t="n">
-        <v>158</v>
+        <v>401</v>
       </c>
       <c r="V2" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="W2" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_FMRAD/rwd-only</t>
+          <t>RWD_DP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6514876632801163</v>
+        <v>0.7661854768153982</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09281390242852272</v>
+        <v>0.06866451469555335</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3045709504133773</v>
+        <v>0.6068715710807751</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1666382045763946</v>
+        <v>0.07728551212340333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4164556962025316</v>
+        <v>0.6874994279228565</v>
       </c>
       <c r="G3" t="n">
-        <v>0.470370276914116</v>
+        <v>0.2011171509829831</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6518987341772152</v>
+        <v>0.6618509212730319</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4763683181692079</v>
+        <v>0.2224948499030437</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6200000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2826729697967488</v>
+        <v>0.2503394570444484</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4137931034482759</v>
+        <v>0.5241228070175439</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.48</v>
       </c>
       <c r="N3" t="n">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6479999999999997</v>
+        <v>0.6515151515151514</v>
       </c>
       <c r="P3" t="n">
-        <v>0.317780221974885</v>
+        <v>0.2192312230012419</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6103896103896104</v>
+        <v>0.4378860672614963</v>
       </c>
       <c r="R3" t="n">
-        <v>0.84</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="V3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="W3" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP_FMRAD</t>
+          <t>RWD_DP/rwd-only</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9066820276497696</v>
+        <v>0.7203083989501313</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05962995200565036</v>
+        <v>0.07244547662529199</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7235192504757723</v>
+        <v>0.3406816706361953</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1117577387166165</v>
+        <v>0.1829663821161361</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6705128205128206</v>
+        <v>0.1168806997952727</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07119224832931163</v>
+        <v>0.1566553091074417</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8962962962962964</v>
+        <v>0.9404163675520459</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1141885821712992</v>
+        <v>0.0704396070181541</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1666666666666665</v>
+        <v>0.8200000000000003</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2390035292236633</v>
+        <v>0.2174639510702185</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2455026455026455</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.7348484848484849</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2101625284537976</v>
+      </c>
       <c r="Q4" t="n">
-        <v>0.3448275862068966</v>
+        <v>0.1657754010695187</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="V4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="W4" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>RWD_FMRAD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8218432510885341</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.07103369217978195</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6725252143594443</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.04976280497231454</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7917939764295068</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1405865825907438</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6269068484258358</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.184198400342047</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2494158561708674</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4591104734576757</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.3254563327840967</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.4886363636363636</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>158</v>
+      </c>
+      <c r="V5" t="n">
+        <v>29</v>
+      </c>
+      <c r="W5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6514876632801163</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.09281390242852272</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3045709504133773</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1666382045763946</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4164556962025316</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.470370276914116</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6518987341772152</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4763683181692079</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2826729697967488</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4137931034482759</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6479999999999997</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.317780221974885</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.6103896103896104</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="n">
+        <v>158</v>
+      </c>
+      <c r="V6" t="n">
+        <v>29</v>
+      </c>
+      <c r="W6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7541075429424944</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.07791122027636677</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.58464416483826</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05436110743421402</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6568839451242121</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1976032561388378</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6210918114143921</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2020926234796748</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5654761904761905</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2499259533753824</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5421052631578948</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5760000000000001</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2180645277322724</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.4993581514762516</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>155</v>
+      </c>
+      <c r="V7" t="n">
+        <v>29</v>
+      </c>
+      <c r="W7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6672890216579537</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.09175754415611526</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4018312927438184</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.08221259037950832</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4849556297120258</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3323673584861938</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5953956437827405</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.393195712342448</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5892857142857142</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2934888810046798</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4596273291925466</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6880000000000002</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2537983087126451</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5341614906832298</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
+        <v>155</v>
+      </c>
+      <c r="V8" t="n">
+        <v>29</v>
+      </c>
+      <c r="W8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9066820276497696</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.05962995200565036</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7235192504757723</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1117577387166165</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6705128205128206</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.07119224832931163</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8962962962962964</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1141885821712992</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2390035292236633</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>0.3448275862068966</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>90</v>
+      </c>
+      <c r="V9" t="n">
+        <v>17</v>
+      </c>
+      <c r="W9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B10" t="n">
         <v>0.6437211981566819</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C10" t="n">
         <v>0.1143470001609829</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D10" t="n">
         <v>0.2318664717348928</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E10" t="n">
         <v>0.06303728097254005</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J10" t="n">
         <v>0.964285714285714</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K10" t="n">
         <v>0.0528564997239297</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L10" t="n">
         <v>0.2245614035087719</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M10" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R10" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T10" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U10" t="n">
         <v>90</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V10" t="n">
         <v>17</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W10" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8011904761904762</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.102151981149015</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6367188501795004</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.06929325677001812</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6790956439393939</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1889859701064079</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7601239669421488</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2584585771885022</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.3556318101242262</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>0.391025641025641</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>88</v>
+      </c>
+      <c r="V11" t="n">
+        <v>17</v>
+      </c>
+      <c r="W11" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6672619047619048</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1272813759888645</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2963053422612246</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1546818549471366</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3835227272727273</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4521867066437151</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4344021571767107</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9523809523809526</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.07598348455812975</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6136363636363636</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>0.356923076923077</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>88</v>
+      </c>
+      <c r="V12" t="n">
+        <v>17</v>
+      </c>
+      <c r="W12" t="n">
         <v>19</v>
       </c>
     </row>
